--- a/examples/sample_output/GOLDEN-DEMO/DataBossX_Report.xlsx
+++ b/examples/sample_output/GOLDEN-DEMO/DataBossX_Report.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runsheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mineral Ownership" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Division of Interest" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defects" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abstract" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mineral Ownership" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Division of Interest" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defects" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -78,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -88,6 +93,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -503,7 +509,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-18 04:24:32 UTC</t>
+          <t>2026-07-18 15:45:31 UTC</t>
         </is>
       </c>
     </row>
@@ -1046,6 +1052,416 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chain-of-title abstract -- ownership chain per tract</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Tract</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Instrument Date</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Doc Type</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Grantor</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Grantee</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Instrument Number</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Conveyed</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Retained</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Net Mineral Acres</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TRACT: Sec 31 T12N R24W</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SEC31T12NR24W</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2018-01-15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mineral Deed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UNITED STATES OF AMERICA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AVERY MINERALS LLC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2018-0001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>80.0000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Runsheet: Recorded Bk 100 Pg 1; patent chain origin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SEC31T12NR24W</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2019-03-02</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mineral Deed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AVERY MINERALS LLC</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BRAND ROYALTY LP</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2019-0002</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>40.0000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Runsheet: Recorded Bk 210 Pg 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SEC31T12NR24W</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2020-06-10</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>BRAND ROYALTY LP</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>CEDAR OPERATING INC</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2020-0003</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>80.0000</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Needs Examiner Review</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Chain break: OGL instrument never referenced in the runsheet; Grantor conveyed 1/2 but only held 1/4 (over-conveyance of 1/4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>TRACT: Sec 32 T12N R24W</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SEC32T12NR24W</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>STATE OF SYNTHETICA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DELTA FAMILY TRUST</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2017-0100</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>60.0000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Runsheet: Recorded Bk 90 Pg 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SEC32T12NR24W</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2021-11-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DELTA FAMILY TRUST</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ECHO ENERGY LLC</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2021-0101</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20.0000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Runsheet: Recorded Bk 305 Pg 88</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1387,7 +1803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1728,36 +2144,36 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Sec 31 T12N R24W</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>0.75000000</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>0.75000000</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>WI &amp; NRI totals</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1944,36 +2360,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Sec 32 T12N R24W</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>1.00000000</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>1.00000000</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>WI &amp; NRI totals</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1983,7 +2399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2149,7 +2565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2326,7 +2742,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58ae1ac0b755fe943999346d3b0de4616dcba609f6d4ea729cb39d0f23e292fc</t>
+          <t>b12c179213f4c28907d305f68b8f7543911a3f16c6c7c0d6393d292e570c17c1</t>
         </is>
       </c>
       <c r="D7" t="n">

--- a/examples/sample_output/GOLDEN-DEMO/DataBossX_Report.xlsx
+++ b/examples/sample_output/GOLDEN-DEMO/DataBossX_Report.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-18 15:45:31 UTC</t>
+          <t>2026-07-18 16:38:09 UTC</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>b12c179213f4c28907d305f68b8f7543911a3f16c6c7c0d6393d292e570c17c1</t>
+          <t>9591ac7a23c63b0479e7b1a84d3226cf942c40ae8a10e6da082c538852edab32</t>
         </is>
       </c>
       <c r="D7" t="n">

--- a/examples/sample_output/GOLDEN-DEMO/DataBossX_Report.xlsx
+++ b/examples/sample_output/GOLDEN-DEMO/DataBossX_Report.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-18 16:38:09 UTC</t>
+          <t>2026-07-18 16:48:10 UTC</t>
         </is>
       </c>
     </row>
@@ -2405,20 +2405,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Defects &amp; missing evidence -- resolve before release</t>
+          <t>Defects &amp; curative worklist -- resolve before release</t>
         </is>
       </c>
     </row>
@@ -2445,6 +2446,11 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>Curative Action</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -2472,6 +2478,11 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>Over-conveyance: the grantor purported to convey more than the record shows they held. Confirm the grantor's actual interest and whether a prior conveyance or reservation is missing from the chain before relying on any downstream interest.</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>runsheet chain</t>
         </is>
       </c>
@@ -2499,6 +2510,11 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>Locate the instrument (or its recording data) that links this document across the OGL register and the runsheet. If none exists, document the gap and obtain the missing conveyance.</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>OGL/runsheet cross-ref</t>
         </is>
       </c>
@@ -2526,6 +2542,11 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>Locate the instrument (or its recording data) that links this document across the OGL register and the runsheet. If none exists, document the gap and obtain the missing conveyance.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>OGL/runsheet cross-ref</t>
         </is>
       </c>
@@ -2553,13 +2574,18 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>Reconcile the mineral estate to a full 8/8: find the instrument(s) that convey the missing or excess undivided interest, or confirm and record an outstanding unleased interest.</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>division of interest</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2742,7 +2768,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9591ac7a23c63b0479e7b1a84d3226cf942c40ae8a10e6da082c538852edab32</t>
+          <t>4cf7a3ce55455c4983b7b5e39acf3ab7068b1191aa65353fd40fb2827ce44b07</t>
         </is>
       </c>
       <c r="D7" t="n">

--- a/examples/sample_output/GOLDEN-DEMO/DataBossX_Report.xlsx
+++ b/examples/sample_output/GOLDEN-DEMO/DataBossX_Report.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-18 16:48:10 UTC</t>
+          <t>2026-07-20 21:19:16 UTC</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC31T12NR24W</t>
+          <t>31-12N-24W</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1208,7 +1208,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC31T12NR24W</t>
+          <t>31-12N-24W</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1268,7 +1268,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SEC31T12NR24W</t>
+          <t>31-12N-24W</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1331,7 +1331,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEC32T12NR24W</t>
+          <t>32-12N-24W</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1391,7 +1391,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEC32T12NR24W</t>
+          <t>32-12N-24W</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2768,11 +2768,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4cf7a3ce55455c4983b7b5e39acf3ab7068b1191aa65353fd40fb2827ce44b07</t>
+          <t>ce57cd4a6593535ddae992bf889b343e0ec405ccdc740a4c3b3bea0ba720f8e6</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6828</v>
+        <v>6827</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
